--- a/src/data/analisis_final.xlsx
+++ b/src/data/analisis_final.xlsx
@@ -1768,14 +1768,14 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C8" t="n">
-        <v>2500</v>
+        <v>21250</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Norte</t>
+          <t>Este</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -1787,11 +1787,11 @@
         <v>1</v>
       </c>
       <c r="G8" t="n">
-        <v>30000</v>
+        <v>255000</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Estandar</t>
+          <t>Premium</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1805,59 +1805,59 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>Bajo</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="L8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C9" t="n">
-        <v>21250</v>
+        <v>4000</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Este</t>
+          <t>Sur</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
       <c r="F9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>255000</v>
+        <v>48000</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Premium</t>
+          <t>Estandar</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Activo</t>
+          <t>Inactivo</t>
         </is>
       </c>
       <c r="K9" t="n">
-        <v>1</v>
-      </c>
-      <c r="L9" t="inlineStr"/>
+        <v>0.08</v>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>Medio</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
